--- a/MiniTemplate/Datas/level.xlsx
+++ b/MiniTemplate/Datas/level.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\Cyber\Demo-Cyber\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD8F937-3647-47C1-BD7D-9716F3C3CC7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6A25CF-B090-41D6-9D74-FC942FB96432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -408,19 +408,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="7.109375" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" customWidth="1"/>
-    <col min="4" max="4" width="87.6640625" customWidth="1"/>
+    <col min="2" max="2" width="7.125" customWidth="1"/>
+    <col min="3" max="3" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="87.625" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="11.77734375" customWidth="1"/>
-    <col min="8" max="8" width="43.5546875" customWidth="1"/>
-    <col min="9" max="9" width="8.44140625" customWidth="1"/>
+    <col min="7" max="7" width="11.75" customWidth="1"/>
+    <col min="8" max="8" width="43.5" customWidth="1"/>
+    <col min="9" max="9" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -434,7 +434,7 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -448,7 +448,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -462,7 +462,7 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -476,7 +476,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>1</v>
       </c>
@@ -485,16 +485,16 @@
       </c>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" s="2">
-        <v>300</v>
+        <v>140</v>
       </c>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>3</v>
       </c>
@@ -503,7 +503,7 @@
       </c>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>4</v>
       </c>
@@ -513,7 +513,7 @@
       <c r="D8" s="3"/>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>5</v>
       </c>
@@ -523,7 +523,7 @@
       <c r="D9" s="3"/>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>6</v>
       </c>
@@ -533,7 +533,7 @@
       <c r="D10" s="3"/>
       <c r="G10" s="1"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>7</v>
       </c>
@@ -543,7 +543,7 @@
       <c r="D11" s="1"/>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>8</v>
       </c>
@@ -553,7 +553,7 @@
       <c r="D12" s="1"/>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>9</v>
       </c>
@@ -563,7 +563,7 @@
       <c r="D13" s="1"/>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>10</v>
       </c>
@@ -573,63 +573,63 @@
       <c r="D14" s="1"/>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D15" s="1"/>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D16" s="1"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D17" s="1"/>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D18" s="1"/>
       <c r="G18" s="1"/>
     </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D19" s="1"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D20" s="1"/>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D21" s="1"/>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D22" s="1"/>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D23" s="1"/>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D25" s="1"/>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D26" s="1"/>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D27" s="1"/>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D28" s="1"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="4:7" x14ac:dyDescent="0.2">
       <c r="G29" s="1"/>
     </row>
   </sheetData>
